--- a/media/Levels/Object.xlsx
+++ b/media/Levels/Object.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\surai\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\A版\Uoh\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E78640BB-5B9F-4084-B9C8-0CE2FEFDC5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB89243-DC87-4D35-93FF-8AF02CC760F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8505" yWindow="3330" windowWidth="28800" windowHeight="15285" xr2:uid="{35648AD5-335E-49FB-ADD2-483CA4E5245F}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{35648AD5-335E-49FB-ADD2-483CA4E5245F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -414,407 +414,327 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F58106-66EA-4C6F-B62D-1D9D15C40A99}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C1">
+        <v>0</v>
+      </c>
+      <c r="D1">
+        <v>0</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
+      <c r="F1">
+        <v>0</v>
+      </c>
+      <c r="G1">
+        <v>0</v>
+      </c>
+      <c r="H1">
+        <v>0</v>
+      </c>
+      <c r="I1">
+        <v>0</v>
+      </c>
+      <c r="J1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>0</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>0</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>0</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>0</v>
       </c>
       <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>0</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>0</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>0</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>0</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14">
-        <v>0</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15">
-        <v>0</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17">
-        <v>0</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18">
-        <v>0</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19">
-        <v>0</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>0</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22">
-        <v>0</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23">
-        <v>0</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25">
-        <v>0</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26">
-        <v>0</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27">
-        <v>0</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28">
-        <v>1</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29">
-        <v>0</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30">
-        <v>0</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31">
-        <v>0</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A32">
-        <v>0</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33">
-        <v>0</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35">
-        <v>0</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36">
-        <v>0</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37">
-        <v>0</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38">
-        <v>0</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39">
-        <v>1</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40">
-        <v>0</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A41">
-        <v>0</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A42">
-        <v>0</v>
-      </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A43">
-        <v>0</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A44">
-        <v>0</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A45">
-        <v>0</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A46">
-        <v>1</v>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A47">
-        <v>0</v>
-      </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A48">
-        <v>0</v>
-      </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A49">
-        <v>0</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A50">
-        <v>1</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
